--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,9 +114,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,14 +494,14 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,12 +517,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>رقم القطعة بالخطة</t>
+          <t>#</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>عنوان القطعة / الكابشن</t>
+          <t>عنوان القطعة كما في ملف الخطة</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -552,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -565,17 +562,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ليش طلبوا منك Ferritin مو بس حديد؟</t>
+          <t>دخلت وسحبت دم… وخلص؟ (رحلة العينة)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -585,50 +582,54 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>تصميم سابين post 1.jpg · instagram.com/dr.nourlab/p/DcIuKQlFnDQ/</t>
+          <t>تصميم سابين post 1.jpg · instagram.com/dr.nourlab/p/DaH1aTeCKBS/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>خطة تموز</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>TSH طبيعي… ولسا في مشكلة؟</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>تصميم سابين مسلَّم على تلغرام — لا مقابل له على إنستغرام</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>فيكن تطلعولي النتيجة أسرع؟ (يوميات المخبر)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 2.jpg · instagram.com/dr.nourlab/p/DafleaOCJX4/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +642,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>في تحليل بيتأثر لو بس شربت قهوة</t>
+          <t>الخوف مو من الإبرة… الخوف من الرقم</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -661,14 +662,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>instagram.com/dr.nourlab/p/DcbKP3UiMUs/ «فنجان القهوة الصغير»</t>
+          <t>تصميم سابين post 3.jpg · instagram.com/dr.nourlab/p/DaulD4AiJnX/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,17 +682,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Vitamin D مو رقم ثابت</t>
+          <t>لو نتائجك بتقدر تحكي هيك رح تقول</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -701,86 +702,94 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>instagram.com/dr.nourlab/p/DctQH9FCNiF/ «Vitamin D مو مجرد رقم»</t>
+          <t>تصميم سابين post 4.jpg · instagram.com/dr.nourlab/p/DbGLoaYiGHA/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>خطة تموز</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>الفرق بين CBC و CRP</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>تصميم سابين مسلَّم — لا مقابل له على إنستغرام</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>وراء كل نتيجة… قرار</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 5.jpg · instagram.com/dr.nourlab/p/DbNfkO0iHZR/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>خطة تموز</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>تحليل PSA وصحة البروستات</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>تصميم سابين مسلَّم — لا مقابل له على إنستغرام</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>مو كل تحليل بينعمل مرة وحدة</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 6.jpg · instagram.com/dr.nourlab/p/Dbk2RahCAmM/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -789,21 +798,17 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>العطش مو دايماً بسبب الحر (تصوير/الدكتورة)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
+          <t>الدقة بالتشخيص بتبدأ من اختيار التحليل الصح</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -813,14 +818,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>تصوير ماجد dr.nour july plan 1_1.mp4 · instagram.com/dr.nourlab/reel/DbamRntNz7H/</t>
+          <t>instagram.com/dr.nourlab/reel/DZ4eE9KtPZT/ — ملف الخطة للبوستات فقط، فلا عنوان مرجعي للريلات</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -829,21 +834,17 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>لسا عم تاخد التشخيص من الـAi؟ (funny — مايكل وسارة)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
+          <t>مو الغرض التشكيك بصحتك</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -853,46 +854,50 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 3-8.mp4 · instagram.com/dr.nourlab/reel/DcQrlgbt-g7/</t>
+          <t>instagram.com/dr.nourlab/reel/DaSyFToNqOM/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>خطة تموز</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>مو كل مشكلة شعر حلها شامبو (Voice Over)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>ناقص</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>لا تصوير ولا مونتاج ولا نشر</t>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>مو كل تحليل بنعمله للإطمئنان</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/dr.nourlab/reel/DakrsGctSSu/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>خطة تموز</t>
+          <t>خطة حزيران</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -901,21 +906,17 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>الإشارة صغيرة… بس معناها كبير (مغنيزيوم)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
+          <t>التفاصيل الصغيرة بتفرق… حتى (الساعة)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -925,7 +926,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>تصوير ماجد dr.nour july plan 2_1.mp4 · instagram.com/dr.nourlab/reel/DbstcAMt6mQ/</t>
+          <t>instagram.com/dr.nourlab/reel/Da7h_w7t-oo/ — كابشن نوال ١٨/٧</t>
         </is>
       </c>
     </row>
@@ -937,25 +938,25 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ريل</t>
+          <t>بوست</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>مو كل كدمة عادية (CBC)</t>
+          <t>ليش طلبوا منك Ferritin مو بس حديد؟</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -965,105 +966,113 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>مونتاج أليسار «مخبر تحليل cbc July 3rd reel.mp4» · instagram.com/dr.nourlab/reel/Db5lg_XNFS6/</t>
+          <t>تصميم سابين post 1.jpg · instagram.com/dr.nourlab/p/DcIuKQlFnDQ/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ريل</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>النعاس مو دايماً كسل (مقاومة الأنسولين)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>ناقص</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>لا تصوير ولا مونتاج ولا نشر</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>TSH طبيعي… ولسا في مشكلة؟</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 2.jpg — لا مقابل له على إنستغرام</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>إعادات تموز</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ريل</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>B12 — أعراض عصبية (إعادة)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>مونتاج أليسار mkhbar 5-8.mp4</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>في تحليل بيتأثر لو بس شربت قهوة</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 3.jpg · instagram.com/dr.nourlab/p/DcbKP3UiMUs/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>إعادات تموز</t>
+          <t>خطة تموز</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ريل</t>
+          <t>بوست</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Vitamin D (إعادة)</t>
+          <t>Vitamin D مو رقم ثابت</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1073,32 +1082,32 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 4-8.mov · instagram.com/dr.nourlab/reel/DcgT8ZKNHHY/</t>
+          <t>تصميم سابين post 4.jpg · instagram.com/dr.nourlab/p/DctQH9FCNiF/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>إعادات تموز</t>
+          <t>خطة تموز</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ريل</t>
+          <t>بوست</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>بديل «القيم الطبيعية» — الدكتورة لم توافق على الإعادة</t>
+          <t>الفرق بين CBC و CRP</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr"/>
@@ -1109,109 +1118,381 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 6-8.mp4 — وصل ٣/٩ الساعة 14:26</t>
+          <t>تصميم سابين post 5.jpg (أُعيد إرساله ٢٥/٧) — لا مقابل له على إنستغرام</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>تحليل PSA وصحة البروستات</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>تصميم سابين post 6.jpg — لا مقابل له على إنستغرام</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>العطش مو دايماً بسبب الحر (تصوير/الدكتورة)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>تصوير ماجد dr.nour july plan 1_1.mp4 · instagram.com/dr.nourlab/reel/DbamRntNz7H/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>لسا عم تاخد التشخيص من الـAi؟ (funny — مايكل وسارة)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 3-8.mp4 · instagram.com/dr.nourlab/reel/DcQrlgbt-g7/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>مو كل مشكلة شعر حلها شامبو (Voice Over)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>ناقص</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>لا تصوير ولا مونتاج ولا نشر</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>الإشارة صغيرة… بس معناها كبير (مغنيزيوم)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>تصوير ماجد dr.nour july plan 2_1.mp4 · instagram.com/dr.nourlab/reel/DbstcAMt6mQ/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>مو كل كدمة عادية (CBC)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار «مخبر تحليل cbc July 3rd reel.mp4» · instagram.com/dr.nourlab/reel/Db5lg_XNFS6/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>خطة تموز</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>النعاس مو دايماً كسل (مقاومة الأنسولين)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>ناقص</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>لا تصوير ولا مونتاج ولا نشر</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>سدّ نقص ٦ و٧</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>B12 — أعراض عصبية (تنميل ووخز)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 5-8.mp4 — جاهز منذ ٢٥/٨ ولم يُنشر</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>سدّ نقص ٦ و٧</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Vitamin D — «طبيعي» لا يعني مثالي</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 4-8.mov · instagram.com/dr.nourlab/reel/DcgT8ZKNHHY/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>سدّ نقص ٦ و٧</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>القيم الطبيعية (Reference Range) — استُبدل بريل آخر</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>الدكتورة لم توافق على الإعادة فاستُبدل · مونتاج أليسار mkhbar 6-8.mp4 وصل ٣/٩ الساعة 14:26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H26"/>
@@ -1225,10 +1506,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -1269,156 +1550,210 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E2" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F2" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ناقص")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>خطة حزيران</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F3" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ناقص")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D4" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ناقص")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>إعادات تموز</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="D5" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ناقص")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>سدّ نقص ٦ و٧</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="D6" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F6" s="5">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ناقص")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7">
-        <f>SUM(C2:C4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="7">
-        <f>SUM(D2:D4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="7">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="7">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6">
+        <f>SUM(C2:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
+        <f>SUM(D2:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="6">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>• المطابقة **بالمحتوى** مع ملف الخطة «المخبر - July Plan-.docx» (أرسلته نوال ١/٧) وملف البوستات (١٦/٨).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>• إعادات التصوير الثلاث من «3 Reels For Shooting.pdf» (أرسله عمر ٣/٨): B12 · Vitamin D · القيم الطبيعية.</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي يعني لا تسليم مسجَّل.</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>• دورة حزيران: لا يوجد ملف خطة لها، فما فيها إلا ما نُشر فعلاً — سبع قطع، بلا سقف معروف.</t>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>• ثلاثة بوستات نُشرت في تموز وآب لا مقابل لها في ملف الخطة — محتوى خارج الخطة.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>• لا توجد خطة آب أصلاً؛ كل ما نُشر بعد ١٥/٨ هو تأخير من خطة تموز (قرار القائدة ٣/٩).</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧ — واحد نُشر، وواحد جاهز، وواحد استُبدل ووصل بديله ٣/٩.</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -48,7 +48,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,6 +119,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1403,7 +1411,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -1414,7 +1422,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 5-8.mp4 — جاهز منذ ٢٥/٨ ولم يُنشر</t>
+          <t>النسخة الأولى mkhbar 5-8.mp4 (٢٥/٨) احتاجت إعادة، والبديل النهائي mkhbar 6-8.mp4 وصل من أليسار ٣/٩ الساعة 14:26 — هو القطعة الوحيدة الجاهزة المتبقّية من الريلات</t>
         </is>
       </c>
     </row>
@@ -1459,38 +1467,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>القيم الطبيعية (Reference Range) — استُبدل بريل آخر</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>الدكتورة لم توافق على الإعادة فاستُبدل · مونتاج أليسار mkhbar 6-8.mp4 وصل ٣/٩ الساعة 14:26</t>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>القيم الطبيعية (Reference Range)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>ملغى</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>الدكتورة لم توافق على إعادته، فلم يُنفَّذ ولا يُنتظر — قرار القائدة (٣/٩)</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1515,6 +1519,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1548,212 +1553,241 @@
           <t>ناقص</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ملغى</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
+      <c r="G2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ملغى")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
+      <c r="G3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ملغى")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
+      <c r="G4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ملغى")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
+      <c r="G5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ملغى")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
+      <c r="G6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ملغى")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7">
         <f>SUM(C2:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <f>SUM(D2:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>SUM(E2:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f>SUM(F2:F6)</f>
         <v/>
       </c>
+      <c r="G7" s="7">
+        <f>SUM(G2:G6)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧ — واحد نُشر، وواحد جاهز، وواحد استُبدل ووصل بديله ٣/٩.</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر · B12 أُعيد ووصل بديله ٣/٩ وهو الجاهز الوحيد · القيم الطبيعية أُلغي لأن الدكتورة لم توافق على إعادته.</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -48,7 +48,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,9 +114,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1262,7 +1254,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>مو كل مشكلة شعر حلها شامبو (Voice Over)</t>
+          <t>إذا ما فيك تروح عالمخبر… مخبرنا بيجي لعندك (سحب خارجي / خدمة منزلية)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -1274,7 +1266,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>لا تصوير ولا مونتاج ولا نشر</t>
+          <t>من ملف الخطة صف ٩، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1366,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>النعاس مو دايماً كسل (مقاومة الأنسولين)</t>
+          <t>بتنعس مباشرة بعد الأكل؟ (مقاومة الإنسولين)</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1386,7 +1378,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>لا تصوير ولا مونتاج ولا نشر</t>
+          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1403,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -1422,7 +1414,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>النسخة الأولى mkhbar 5-8.mp4 (٢٥/٨) احتاجت إعادة، والبديل النهائي mkhbar 6-8.mp4 وصل من أليسار ٣/٩ الساعة 14:26 — هو القطعة الوحيدة الجاهزة المتبقّية من الريلات</t>
+          <t>مونتاج أليسار mkhbar 5-8.mp4 (٢٥/٨) · كرتا «إعادة تصوير ريل: تحليل B12» و«مونتاج: تحليل B12» مقفلان على اللوح</t>
         </is>
       </c>
     </row>
@@ -1467,34 +1459,38 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>القيم الطبيعية (Reference Range)</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>ملغى</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>الدكتورة لم توافق على إعادته، فلم يُنفَّذ ولا يُنتظر — قرار القائدة (٣/٩)</t>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>بديل «القيم الطبيعية» — الدكتورة لم توافق على إعادة الأصلي</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 6-8.mp4 وصل ٣/٩ الساعة 14:26 · قرار القائدة (٣/٩): التصوير والمونتاج جاهزان فيُقفل كرتا ماجد وأليسار</t>
         </is>
       </c>
     </row>
@@ -1560,234 +1556,234 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ملغى")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ملغى")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ملغى")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ملغى")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"منشور")</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
         <v/>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ناقص")</f>
         <v/>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ملغى")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6">
         <f>SUM(C2:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <f>SUM(D2:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <f>SUM(E2:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <f>SUM(F2:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <f>SUM(G2:G6)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر · B12 أُعيد ووصل بديله ٣/٩ وهو الجاهز الوحيد · القيم الطبيعية أُلغي لأن الدكتورة لم توافق على إعادته.</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر ٢٦/٨ · B12 جاهز من ٢٥/٨ · بديل «القيم الطبيعية» جاهز من ٣/٩. فالجاهز غير المنشور من الريلات اتنين.</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الجرد" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخّص" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الدورات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +49,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +74,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF6"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +127,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -125,6 +142,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1266,7 +1289,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>من ملف الخطة صف ٩، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر</t>
+          <t>من ملف الخطة صف ٩، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. مسدود: القائدة لنوال ٢٦/٨ «بس ريلات بدون الدكتورة… مابدها تطلع بالريلات هالفترة»</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1369,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>مونتاج أليسار «مخبر تحليل cbc July 3rd reel.mp4» · instagram.com/dr.nourlab/reel/Db5lg_XNFS6/</t>
+          <t>instagram.com/dr.nourlab/reel/Db5lg_XNFS6/ — المونتاج إما «مخبر تحليل cbc July 3rd reel.mp4» (٢٨/٧) أو أحد ملفَّي ١٠/٨؛ غير محسوم</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1401,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر</t>
+          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. مسدود لنفس السبب (قرار الدكتورة ٢٦/٨)</t>
         </is>
       </c>
     </row>
@@ -1494,8 +1517,148 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>هل كل ارتفاع بالكوليسترول خطر؟ (HDL / LDL)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>منشور</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/dr.nourlab/p/DZpEH5gCIyH/ — منشور داخل دورة حزيران وما إله مقابل بملف الخطة، فبينعدّ بدل</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>مونتاج mkhbar 1-8.mp4</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>غير محسوم</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>وصل مع 2-8 بنفس اليوم؛ واحد من الاتنين نُشر ١١/٨ (CBC) والتاني بلا مقابل منشور — ما في شي يفصل بينهن</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>مونتاج mkhbar 2-8.mp4</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>غير محسوم</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>نفس الملاحظة — واحد من هالاتنين جاهز غير منشور</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ريل اللوكيشن — بلا صوت ولا أشخاص، إشارات وموسيقى</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>قيد التنفيذ</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>طلب الدكتورة عبر عمر بالمجموعة ٣/٩ ٨:٥٤، وأليسار «اوكي». إضافة خارج الخطة وما إله كرت على اللوح</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1506,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1516,6 +1679,8 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1554,236 +1719,532 @@
           <t>ملغى</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>غير محسوم</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>قيد التنفيذ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E2" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F2" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G2" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A2,الجرد!$B$2:$B$26,$B2,الجرد!$G$2:$G$26,"ملغى")</f>
+      <c r="D2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I2" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E3" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F3" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A3,الجرد!$B$2:$B$26,$B3,الجرد!$G$2:$G$26,"ملغى")</f>
+      <c r="D3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I3" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E4" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F4" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A4,الجرد!$B$2:$B$26,$B4,الجرد!$G$2:$G$26,"ملغى")</f>
+      <c r="D4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I4" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E5" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F5" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A5,الجرد!$B$2:$B$26,$B5,الجرد!$G$2:$G$26,"ملغى")</f>
+      <c r="D5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I5" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E6" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F6" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>COUNTIFS(الجرد!$A$2:$A$26,$A6,الجرد!$B$2:$B$26,$B6,الجرد!$G$2:$G$26,"ملغى")</f>
+      <c r="D6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I6" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I7" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6">
-        <f>SUM(C2:C6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>SUM(D2:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>SUM(G2:G6)</f>
-        <v/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="8">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="8">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="8">
+        <f>SUM(H2:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="8">
+        <f>SUM(I2:I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر ٢٦/٨ · B12 جاهز من ٢٥/٨ · بديل «القيم الطبيعية» جاهز من ٣/٩. فالجاهز غير المنشور من الريلات اتنين.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>بوست</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>الشرح</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>المستحقّ — ٣ دورات × ٦</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>الدورات: ١٥/٦→١٥/٧ · ١٥/٧→١٥/٨ · ١٥/٨→١٥/٩. الخطة ٦ ريل + ٦ بوست لكل دورة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>المنشور فعلاً</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>ريلات: ٢٢/٦ · ٢/٧ · ٩/٧ · ١٨/٧ · ٣٠/٧ · ٦/٨ · ١١/٨ · ٢٠/٨ · ٢٦/٨ — بوستات: ١٦/٦ · ٢٨/٦ · ٧/٧ · ١٣/٧ · ٢٢/٧ · ٢٥/٧ · ٣/٨ · ١٧/٨ · ٢٤/٨ · ٣١/٨. آخر منشور على الحساب ٣١/٨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>ريلات: mkhbar 5-8 (B12، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩) · واحد من ملفَّي ١٠/٨. بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>أقصى ما ينثبت إنتاجه</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>المنشور + الجاهز.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>بلا أي أثر — لا تسليم ولا نشر</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>منهن ريل ٩ (الخدمة المنزلية) و١٢ (مقاومة الإنسولين) — تصوير مع الدكتورة، ومسدودان بقرارها (٢٦/٨: «ريلات بدون الدكتورة»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>قيود على القراءة</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر ٢٦/٨ · B12 جاهز من ٢٥/٨ · بديل «القيم الطبيعية» جاهز من ٣/٩. فالجاهز غير المنشور من الريلات اتنين.</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الدورات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -74,11 +74,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6E0EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,9 +123,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -514,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1262,34 +1254,38 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>إذا ما فيك تروح عالمخبر… مخبرنا بيجي لعندك (سحب خارجي / خدمة منزلية)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>ناقص</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>من ملف الخطة صف ٩، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. مسدود: القائدة لنوال ٢٦/٨ «بس ريلات بدون الدكتورة… مابدها تطلع بالريلات هالفترة»</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 5-8.mp4 (٢٥/٨) — تحديد القائدة (٣/٩). قطعة خطة أصلية، جاهزة وما انشرت</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1365,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>instagram.com/dr.nourlab/reel/Db5lg_XNFS6/ — المونتاج إما «مخبر تحليل cbc July 3rd reel.mp4» (٢٨/٧) أو أحد ملفَّي ١٠/٨؛ غير محسوم</t>
+          <t>instagram.com/dr.nourlab/reel/Db5lg_XNFS6/ — نُشر ١١/٨، فمونتاجه أحد ملفَّي ١٠/٨ (mkhbar 1-8 أو 2-8) والتاني هو ريل B12</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1397,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. مسدود لنفس السبب (قرار الدكتورة ٢٦/٨)</t>
+          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. الوحيد الناقص باسمه من خطة تموز، ومسدود بقرار الدكتورة (٢٦/٨: «ريلات بدون الدكتورة»)</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -1437,7 +1433,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 5-8.mp4 (٢٥/٨) · كرتا «إعادة تصوير ريل: تحليل B12» و«مونتاج: تحليل B12» مقفلان على اللوح</t>
+          <t>أحد ملفَّي أليسار يوم ١٠/٨ (mkhbar 1-8 أو 2-8) — التاني نُشر ١١/٨ كريل CBC. حلا ٢/٨: «هاد تبع b12 بس ماعندي الملف الأساسي»، وكرتا التصوير والمونتاج مقفلان على اللوح</t>
         </is>
       </c>
     </row>
@@ -1569,96 +1565,24 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>مونتاج mkhbar 1-8.mp4</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
+          <t>ريل اللوكيشن — بلا صوت ولا أشخاص، إشارات وموسيقى</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>غير محسوم</t>
+          <t>قيد التنفيذ</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>وصل مع 2-8 بنفس اليوم؛ واحد من الاتنين نُشر ١١/٨ (CBC) والتاني بلا مقابل منشور — ما في شي يفصل بينهن</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>خارج الخطة</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>ريل</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>مونتاج mkhbar 2-8.mp4</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>غير محسوم</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>نفس الملاحظة — واحد من هالاتنين جاهز غير منشور</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>خارج الخطة</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>ريل</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>ريل اللوكيشن — بلا صوت ولا أشخاص، إشارات وموسيقى</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>قيد التنفيذ</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
           <t>طلب الدكتورة عبر عمر بالمجموعة ٣/٩ ٨:٥٤، وأليسار «اوكي». إضافة خارج الخطة وما إله كرت على اللوح</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1731,358 +1655,358 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I2" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A2,الجرد!$B$2:$B$30,$B2,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>خطة حزيران</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I3" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A3,الجرد!$B$2:$B$30,$B3,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I4" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A4,الجرد!$B$2:$B$30,$B4,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I5" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A5,الجرد!$B$2:$B$30,$B5,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I6" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A6,الجرد!$B$2:$B$30,$B6,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>خارج الخطة</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>بوست</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A7,الجرد!$B$2:$B$30,$B7,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>خارج الخطة</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"منشور")</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"جاهز غير منشور")</f>
-        <v/>
-      </c>
-      <c r="F8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"ناقص")</f>
-        <v/>
-      </c>
-      <c r="G8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"غير محسوم")</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>COUNTIFS(الجرد!$A$2:$A$30,$A8,الجرد!$B$2:$B$30,$B8,الجرد!$G$2:$G$30,"قيد التنفيذ")</f>
+      <c r="D8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"منشور")</f>
+        <v/>
+      </c>
+      <c r="E8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <v/>
+      </c>
+      <c r="F8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ناقص")</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ملغى")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"غير محسوم")</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7">
         <f>SUM(C2:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <f>SUM(D2:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <f>SUM(I2:I8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>• المطابقة **بالمحتوى**: كل سطر عنوانه مأخوذ من ملف الخطة نفسه، لا من العدّ.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>• ملفات الخطط: «المخبر - June Posts.docx» (نوال ٦/٦) · «المخبر - July Plan-.docx» (٢٣/٦ ثم ١/٧) · «3 Scripts For Shooting.pdf» (٢٠/٦ و٢٢/٦).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>• ريلات حزيران بلا ملف خطة (الملف للبوستات فقط)، فعناوينها من كابشناتها المنشورة والمستحق مأخوذ من عدد ما نُشر.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>• «تاريخ الإنتاج» = يوم تسليم الملف على تلغرام. فاضي = لا تسليم مسجَّل.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>• لا توجد خطة آب: كل ما نُشر بعد ١٥/٨ تأخير من خطتَي حزيران وتموز (قرار القائدة ٣/٩).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>• الثلاثة سكريبتات كُتبت في حزيران لسدّ نقص ريلات ٦ و٧: Vitamin D نُشر ٢٦/٨ · B12 جاهز من ٢٥/٨ · بديل «القيم الطبيعية» جاهز من ٣/٩. فالجاهز غير المنشور من الريلات اتنين.</t>
         </is>
@@ -2099,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2131,120 +2055,127 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>المستحقّ — ٣ دورات × ٦</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>الدورات: ١٥/٦→١٥/٧ · ١٥/٧→١٥/٨ · ١٥/٨→١٥/٩. الخطة ٦ ريل + ٦ بوست لكل دورة.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>المنشور فعلاً</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>ريلات: ٢٢/٦ · ٢/٧ · ٩/٧ · ١٨/٧ · ٣٠/٧ · ٦/٨ · ١١/٨ · ٢٠/٨ · ٢٦/٨ — بوستات: ١٦/٦ · ٢٨/٦ · ٧/٧ · ١٣/٧ · ٢٢/٧ · ٢٥/٧ · ٣/٨ · ١٧/٨ · ٢٤/٨ · ٣١/٨. آخر منشور على الحساب ٣١/٨.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>جاهز غير منشور</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>ريلات: mkhbar 5-8 (B12، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩) · واحد من ملفَّي ١٠/٨. بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>ريلات: أحد ملفَّي ١٠/٨ (إعادة B12) · mkhbar 5-8 (ريل ٩ بالخطة — الخدمة المنزلية، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩). بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>أقصى ما ينثبت إنتاجه</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>المنشور + الجاهز.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>بلا أي أثر — لا تسليم ولا نشر</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>منهن ريل ٩ (الخدمة المنزلية) و١٢ (مقاومة الإنسولين) — تصوير مع الدكتورة، ومسدودان بقرارها (٢٦/٨: «ريلات بدون الدكتورة»).</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>الوحيد المعروف باسمه: ريل ١٢ (مقاومة الإنسولين) — تصوير مع الدكتورة ومسدود بقرارها (٢٦/٨: «ريلات بدون الدكتورة»). الباقي فرق دورة حزيران، وما إلها ملف خطة للريلات فما في عناوين تنتسمّى.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>قيود على القراءة</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>• كل المونتاجات الستة من ٢/٨ لليوم صار إلها دلالة: 1-8 و2-8 (ريل ١١ CBC + إعادة B12) · 3-8 (ريل ٨) · 4-8 (إعادة فيتامين د) · 5-8 (ريل ٩) · 6-8 (بديل «القيم الطبيعية»).</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -73,7 +73,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1189,14 +1189,10 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>العطش مو دايماً بسبب الحر (تصوير/الدكتورة)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
+          <t>إذا عم تعطش طول الوقت… مو طبيعي (تصوير/الدكتورة)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -1209,7 +1205,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>تصوير ماجد dr.nour july plan 1_1.mp4 · instagram.com/dr.nourlab/reel/DbamRntNz7H/</t>
+          <t>instagram.com/dr.nourlab/reel/DbamRntNz7H/ — ملف المونتاج غير معروف؛ سلّم قبل نافذة سجلّ تلغرام</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1301,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>الإشارة صغيرة… بس معناها كبير (مغنيزيوم)</t>
+          <t>الإشارة صغيرة… بس معناها كبير (نقص مغنيزيوم)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1325,7 +1321,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>تصوير ماجد dr.nour july plan 2_1.mp4 · instagram.com/dr.nourlab/reel/DbstcAMt6mQ/</t>
+          <t>تصوير ماجد july-2-1 «نقص مغنزيوم» — تحديد القائدة (٣/٩) · instagram.com/dr.nourlab/reel/DbstcAMt6mQ/</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1361,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>instagram.com/dr.nourlab/reel/Db5lg_XNFS6/ — نُشر ١١/٨، فمونتاجه أحد ملفَّي ١٠/٨ (mkhbar 1-8 أو 2-8) والتاني هو ريل B12</t>
+          <t>مونتاج أليسار july-1-3 «عن تحليل CBC» — تحديد القائدة (٣/٩) · instagram.com/dr.nourlab/reel/Db5lg_XNFS6/</t>
         </is>
       </c>
     </row>
@@ -1385,19 +1381,23 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>بتنعس مباشرة بعد الأكل؟ (مقاومة الإنسولين)</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+          <t>بتنعس مباشرة بعد الأكل؟ (مقاومة الإنسولين / ارتفاع السكر)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>ناقص</t>
+          <t>مصوَّر بلا مونتاج</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>من ملف الخطة صف ١٢، تصوير/الدكتورة — لا تصوير ولا مونتاج ولا نشر. الوحيد الناقص باسمه من خطة تموز، ومسدود بقرار الدكتورة (٢٦/٨: «ريلات بدون الدكتورة»)</t>
+          <t>تصوير ماجد july-1-1 «أعراض ومؤشرات لارتفاع السكر» = ريل ١٢ — تحديد القائدة (٣/٩). مصوَّر ومنه ولا مونتاج ولا نشر. ⚠️ القائدة كتبت ١١/٨ «٨ و٩ و١٢ هدول ماتصورو» — فإما اللقطات انرفضت أو الرسالة كانت عن الجاهز مو المصوَّر</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>B12 — أعراض عصبية (تنميل ووخز)</t>
+          <t>B12 — أعراض عصبية (تنميل ووخز بالأطراف)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>أحد ملفَّي أليسار يوم ١٠/٨ (mkhbar 1-8 أو 2-8) — التاني نُشر ١١/٨ كريل CBC. حلا ٢/٨: «هاد تبع b12 بس ماعندي الملف الأساسي»، وكرتا التصوير والمونتاج مقفلان على اللوح</t>
+          <t>مونتاج أليسار mkhbar 2-8.mp4 (١٠/٨) — بيبلّش «في أعراض عصبية سببها ممكن يبين بتحليل الدم» (تحديد القائدة ٣/٩). حلا ٢/٨: «هاد تبع b12 بس ماعندي الملف الأساسي»</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>مونتاج أليسار mkhbar 4-8.mov · instagram.com/dr.nourlab/reel/DcgT8ZKNHHY/</t>
+          <t>أول نسخة mkhbar 1-8.mp4 (١٠/٨، تحديد القائدة ٣/٩) ← تعديلات lv_0 (١٥/٨ «طلبت نزبط بشرتا» و١٧/٨) ← النهائية mkhbar 4-8.mov (٢١/٨) · instagram.com/dr.nourlab/reel/DcgT8ZKNHHY/</t>
         </is>
       </c>
     </row>
@@ -1601,9 +1601,9 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1635,17 +1635,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>مصوَّر بلا مونتاج</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>ناقص</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ملغى</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>غير محسوم</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1677,15 +1677,15 @@
         <v/>
       </c>
       <c r="F2" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G2" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G2" s="6">
+      <c r="H2" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I2" s="6">
@@ -1716,15 +1716,15 @@
         <v/>
       </c>
       <c r="F3" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G3" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I3" s="6">
@@ -1755,15 +1755,15 @@
         <v/>
       </c>
       <c r="F4" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G4" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I4" s="6">
@@ -1794,15 +1794,15 @@
         <v/>
       </c>
       <c r="F5" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G5" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I5" s="6">
@@ -1833,15 +1833,15 @@
         <v/>
       </c>
       <c r="F6" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I6" s="6">
@@ -1872,15 +1872,15 @@
         <v/>
       </c>
       <c r="F7" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I7" s="6">
@@ -1911,15 +1911,15 @@
         <v/>
       </c>
       <c r="F8" s="6">
+        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ناقص")</f>
         <v/>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"غير محسوم")</f>
         <v/>
       </c>
       <c r="I8" s="6">
@@ -2023,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2104,78 +2104,103 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>ريلات: أحد ملفَّي ١٠/٨ (إعادة B12) · mkhbar 5-8 (ريل ٩ بالخطة — الخدمة المنزلية، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩). بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
+          <t>ريلات: mkhbar 2-8 (إعادة B12، ١٠/٨) · mkhbar 5-8 (ريل ٩ — الخدمة المنزلية، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩). بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>مصوَّر بلا مونتاج</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>ريل ١٢ — تصوير ماجد july-1-1 «أعراض ومؤشرات لارتفاع السكر» (٢٦/٧). اللقطات موجودة وما انمنتجت: أقرب شغل جاهز للإقفال.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>أقصى ما ينثبت إنتاجه</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="B6" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>المنشور + الجاهز.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="C6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>المنشور + الجاهز + المصوَّر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>بلا أي أثر — لا تسليم ولا نشر</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>الوحيد المعروف باسمه: ريل ١٢ (مقاومة الإنسولين) — تصوير مع الدكتورة ومسدود بقرارها (٢٦/٨: «ريلات بدون الدكتورة»). الباقي فرق دورة حزيران، وما إلها ملف خطة للريلات فما في عناوين تنتسمّى.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="C7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>كلها فرق **دورة حزيران** — وما إلها ملف خطة للريلات (ملف حزيران للبوستات فقط)، فما في عناوين تنتسمّى ولا مصدر يقول شو كان مفروض ينتصوّر. أما خطة تموز فصار كل ريلاتها الستة إلها أثر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>قيود على القراءة</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
+          <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
+          <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• كل المونتاجات الستة من ٢/٨ لليوم صار إلها دلالة: 1-8 و2-8 (ريل ١١ CBC + إعادة B12) · 3-8 (ريل ٨) · 4-8 (إعادة فيتامين د) · 5-8 (ريل ٩) · 6-8 (بديل «القيم الطبيعية»).</t>
+          <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>• كل مونتاج صار إله دلالة (تحديد القائدة ٣/٩): mkhbar 1-8 و4-8 = فيتامين د (أول نسخة ثم النهائية) · 2-8 = إعادة B12 · 3-8 = ريل ٨ · 5-8 = ريل ٩ · 6-8 = بديل «القيم الطبيعية». ومن تصوير ماجد: july-1-1 = ريل ١٢ · july-2-1 = ريل ١٠ · وأليسار july-1-3 = ريل ١١.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>• ملفات تموز (july-*) مو موجودة بسجلّ تلغرام تبع النظام — نافذته تبلّش ٢/٨. دلالتها من القائدة مباشرة، وهاد مكتوب بسطر الدليل لكل صف.</t>
         </is>
       </c>
     </row>

--- a/docs/cycle-reports/nour-inventory-2026-09.xlsx
+++ b/docs/cycle-reports/nour-inventory-2026-09.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الدورات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الجرد'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -73,7 +73,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1366,38 +1366,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>خطة تموز</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>بتنعس مباشرة بعد الأكل؟ (مقاومة الإنسولين / ارتفاع السكر)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>مصوَّر بلا مونتاج</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>تصوير ماجد july-1-1 «أعراض ومؤشرات لارتفاع السكر» = ريل ١٢ — تحديد القائدة (٣/٩). مصوَّر ومنه ولا مونتاج ولا نشر. ⚠️ القائدة كتبت ١١/٨ «٨ و٩ و١٢ هدول ماتصورو» — فإما اللقطات انرفضت أو الرسالة كانت عن الجاهز مو المصوَّر</t>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>بعتو ماجد july-1-1 «أعراض ومؤشرات لارتفاع السكر» — تحديد القائدة (٣/٩). مسلَّم وجاهز، وما انشر</t>
         </is>
       </c>
     </row>
@@ -1478,38 +1478,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>سدّ نقص ٦ و٧</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>بديل «القيم الطبيعية» — الدكتورة لم توافق على إعادة الأصلي</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>جاهز غير منشور</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>مونتاج أليسار mkhbar 6-8.mp4 وصل ٣/٩ الساعة 14:26 · قرار القائدة (٣/٩): التصوير والمونتاج جاهزان فيُقفل كرتا ماجد وأليسار</t>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>القيم الطبيعية (Reference Range)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ملغى</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>الدكتورة لم توافق على إعادته فلم يُنفَّذ إطلاقاً. الاتفاق بالمجموعة ٨/٨: «بدنا نبدلو بريل تاني… فكرة funny» — والبديل ريل إضافي خارج الخطة (تحديد القائدة ٣/٩)</t>
         </is>
       </c>
     </row>
@@ -1550,39 +1546,75 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>خارج الخطة</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ريل</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>ريل إضافي funny — «ستي كيف بتتخيل عزراييل»</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>جاهز غير منشور</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>مونتاج أليسار mkhbar 6-8.mp4 وصل ٣/٩ الساعة 14:26. **الريل الإضافي** الذي حلّ محلّ «القيم الطبيعية» (تحديد القائدة ٣/٩) — وعليه كرتا ماجد وأليسار المفتوحان باسم «بديل القيم الطبيعية»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>خارج الخطة</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ريل</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>ريل اللوكيشن — بلا صوت ولا أشخاص، إشارات وموسيقى</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>قيد التنفيذ</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>طلب الدكتورة عبر عمر بالمجموعة ٣/٩ ٨:٥٤، وأليسار «اوكي». إضافة خارج الخطة وما إله كرت على اللوح</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1593,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1601,10 +1633,9 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1635,20 +1666,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>مصوَّر بلا مونتاج</t>
+          <t>ناقص</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ناقص</t>
+          <t>ملغى</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ملغى</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>قيد التنفيذ</t>
         </is>
@@ -1669,27 +1695,23 @@
         <v>6</v>
       </c>
       <c r="D2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A2,الجرد!$B$2:$B$29,$B2,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A2,الجرد!$B$2:$B$29,$B2,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A2,الجرد!$B$2:$B$29,$B2,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A2,الجرد!$B$2:$B$29,$B2,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I2" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A2,الجرد!$B$2:$B$28,$B2,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A2,الجرد!$B$2:$B$29,$B2,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1708,27 +1730,23 @@
         <v>4</v>
       </c>
       <c r="D3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A3,الجرد!$B$2:$B$29,$B3,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A3,الجرد!$B$2:$B$29,$B3,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A3,الجرد!$B$2:$B$29,$B3,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A3,الجرد!$B$2:$B$29,$B3,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I3" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A3,الجرد!$B$2:$B$28,$B3,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A3,الجرد!$B$2:$B$29,$B3,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1747,27 +1765,23 @@
         <v>6</v>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A4,الجرد!$B$2:$B$29,$B4,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A4,الجرد!$B$2:$B$29,$B4,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A4,الجرد!$B$2:$B$29,$B4,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A4,الجرد!$B$2:$B$29,$B4,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I4" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A4,الجرد!$B$2:$B$28,$B4,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A4,الجرد!$B$2:$B$29,$B4,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1786,27 +1800,23 @@
         <v>6</v>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A5,الجرد!$B$2:$B$29,$B5,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A5,الجرد!$B$2:$B$29,$B5,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A5,الجرد!$B$2:$B$29,$B5,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A5,الجرد!$B$2:$B$29,$B5,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I5" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A5,الجرد!$B$2:$B$28,$B5,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A5,الجرد!$B$2:$B$29,$B5,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1825,27 +1835,23 @@
         <v>3</v>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A6,الجرد!$B$2:$B$29,$B6,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A6,الجرد!$B$2:$B$29,$B6,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A6,الجرد!$B$2:$B$29,$B6,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A6,الجرد!$B$2:$B$29,$B6,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I6" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A6,الجرد!$B$2:$B$28,$B6,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A6,الجرد!$B$2:$B$29,$B6,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1864,27 +1870,23 @@
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A7,الجرد!$B$2:$B$29,$B7,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A7,الجرد!$B$2:$B$29,$B7,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A7,الجرد!$B$2:$B$29,$B7,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A7,الجرد!$B$2:$B$29,$B7,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A7,الجرد!$B$2:$B$28,$B7,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A7,الجرد!$B$2:$B$29,$B7,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1903,27 +1905,23 @@
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A8,الجرد!$B$2:$B$29,$B8,الجرد!$G$2:$G$29,"منشور")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"جاهز غير منشور")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A8,الجرد!$B$2:$B$29,$B8,الجرد!$G$2:$G$29,"جاهز غير منشور")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"مصوَّر بلا مونتاج")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A8,الجرد!$B$2:$B$29,$B8,الجرد!$G$2:$G$29,"ناقص")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ناقص")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A8,الجرد!$B$2:$B$29,$B8,الجرد!$G$2:$G$29,"ملغى")</f>
         <v/>
       </c>
       <c r="H8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"ملغى")</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>COUNTIFS(الجرد!$A$2:$A$28,$A8,الجرد!$B$2:$B$28,$B8,الجرد!$G$2:$G$28,"قيد التنفيذ")</f>
+        <f>COUNTIFS(الجرد!$A$2:$A$29,$A8,الجرد!$B$2:$B$29,$B8,الجرد!$G$2:$G$29,"قيد التنفيذ")</f>
         <v/>
       </c>
     </row>
@@ -1956,10 +1954,6 @@
       </c>
       <c r="H9" s="7">
         <f>SUM(H2:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>SUM(I2:I8)</f>
         <v/>
       </c>
     </row>
@@ -2023,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2097,108 +2091,90 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>ريلات: mkhbar 2-8 (إعادة B12، ١٠/٨) · mkhbar 5-8 (ريل ٩ — الخدمة المنزلية، ٢٥/٨) · mkhbar 6-8 (بديل «القيم الطبيعية»، ٣/٩). بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
+          <t>ريلات: july-1-1 (ريل ١٢ — ارتفاع السكر، ماجد ٢٦/٧) · mkhbar 2-8 (إعادة B12، ١٠/٨) · mkhbar 5-8 (ريل ٩ — الخدمة المنزلية، ٢٥/٨) · mkhbar 6-8 (الريل الإضافي funny، ٣/٩). بوستات: TSH · CBC/CRP · PSA (تصاميم سابين ١٥/٧ و٢٠/٧).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>مصوَّر بلا مونتاج</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>ريل ١٢ — تصوير ماجد july-1-1 «أعراض ومؤشرات لارتفاع السكر» (٢٦/٧). اللقطات موجودة وما انمنتجت: أقرب شغل جاهز للإقفال.</t>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>أقصى ما ينثبت إنتاجه</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>المنشور + الجاهز.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>أقصى ما ينثبت إنتاجه</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>المنشور + الجاهز + المصوَّر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>بلا أي أثر — لا تسليم ولا نشر</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>كلها فرق **دورة حزيران** — وما إلها ملف خطة للريلات (ملف حزيران للبوستات فقط)، فما في عناوين تنتسمّى ولا مصدر يقول شو كان مفروض ينتصوّر. أما خطة تموز فصار كل ريلاتها الستة إلها أثر.</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>قيود على القراءة</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>قيود على القراءة</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>• قبل ٢/٨ ما في سجلّ تسليمات إطلاقاً: البوت ما كان يراقب والتصدير ما رجع لهناك — فحدّ «١٨ مرسَل» ما بينفحص لحزيران وتموز إلا بالمنشور.</t>
+          <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• الدورة التالتة (من ١٥/٨) ما إلها ملف خطة: القائدة طلبت وحدة من نوال ٢٦/٨ «٦ بوست و٦ ريل».</t>
+          <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• قاعدة القائدة (٣/٩): الزيادة تنعتبر بدل — الدكتورة بتغيّر السكريبت أثناء التصوير وما منغيّر بالخطة. فأي ريل بديل (اللوكيشن، أو funny) بينوب بالعدد عن قطعة مسدودة.</t>
+          <t>• كل مونتاج صار إله دلالة (تحديد القائدة ٣/٩): mkhbar 1-8 و4-8 = فيتامين د (أول نسخة ثم النهائية) · 2-8 = إعادة B12 · 3-8 = ريل ٨ · 5-8 = ريل ٩ · 6-8 = بديل «القيم الطبيعية». ومن تصوير ماجد: july-1-1 = ريل ١٢ · july-2-1 = ريل ١٠ · وأليسار july-1-3 = ريل ١١.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>• كل مونتاج صار إله دلالة (تحديد القائدة ٣/٩): mkhbar 1-8 و4-8 = فيتامين د (أول نسخة ثم النهائية) · 2-8 = إعادة B12 · 3-8 = ريل ٨ · 5-8 = ريل ٩ · 6-8 = بديل «القيم الطبيعية». ومن تصوير ماجد: july-1-1 = ريل ١٢ · july-2-1 = ريل ١٠ · وأليسار july-1-3 = ريل ١١.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>• ملفات تموز (july-*) مو موجودة بسجلّ تلغرام تبع النظام — نافذته تبلّش ٢/٨. دلالتها من القائدة مباشرة، وهاد مكتوب بسطر الدليل لكل صف.</t>
         </is>
